--- a/data/trans_orig/P2A_psíq_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>31049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>30530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57356</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1000837</t>
+          <t>1000674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1018968</t>
+          <t>1018958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1283808</t>
+          <t>1283097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1301661</t>
+          <t>1301491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2289479</t>
+          <t>2291278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2316263</t>
+          <t>2316305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30952</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1676288</t>
+          <t>1676885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1689738</t>
+          <t>1689691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1567992</t>
+          <t>1567785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1581782</t>
+          <t>1582517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3250134</t>
+          <t>3250423</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3268566</t>
+          <t>3268399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546852</t>
+          <t>546801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>462662</t>
+          <t>461557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473249</t>
+          <t>473376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1011578</t>
+          <t>1012512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1023871</t>
+          <t>1024147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53787</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53688</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87187</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3234548</t>
+          <t>3233548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3256780</t>
+          <t>3256393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3325410</t>
+          <t>3325235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3350575</t>
+          <t>3350811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6568554</t>
+          <t>6568379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6602053</t>
+          <t>6601184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>47501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>28656</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53857</t>
+          <t>57538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53527</t>
+          <t>55756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90654</t>
+          <t>91610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>927092</t>
+          <t>927142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>952384</t>
+          <t>952729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1283940</t>
+          <t>1280259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1310141</t>
+          <t>1309141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2221786</t>
+          <t>2220830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2258913</t>
+          <t>2256684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37156</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,42 +2729,42 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>51666</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>38877</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>67580</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>51666</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>38487</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>67610</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1926801</t>
+          <t>1927382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1948192</t>
+          <t>1948521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1719165</t>
+          <t>1718641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739458</t>
+          <t>1739729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,47 +2842,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3442</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3670094</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3654180</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3682883</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,96%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3442</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3670094</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3654150</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3683273</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465466</t>
+          <t>466198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479116</t>
+          <t>479100</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442042</t>
+          <t>442925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454820</t>
+          <t>455570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>915394</t>
+          <t>915142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>931842</t>
+          <t>932866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>46786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82701</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58124</t>
+          <t>58584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93043</t>
+          <t>92279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115084</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163879</t>
+          <t>160047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3337081</t>
+          <t>3334905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3372233</t>
+          <t>3372996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3461187</t>
+          <t>3461951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3496106</t>
+          <t>3495646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6810133</t>
+          <t>6813965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6858928</t>
+          <t>6861854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51289</t>
+          <t>50944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>731261</t>
+          <t>731979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>746203</t>
+          <t>746723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>959354</t>
+          <t>960057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>979276</t>
+          <t>979627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1697718</t>
+          <t>1698063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1722104</t>
+          <t>1722112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41400</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29256</t>
+          <t>31368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59903</t>
+          <t>61181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2048941</t>
+          <t>2051178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2067026</t>
+          <t>2068010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1946900</t>
+          <t>1946740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1969863</t>
+          <t>1969599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4004782</t>
+          <t>4003504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4035429</t>
+          <t>4033317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,77 +4645,77 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5006</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1943</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10976</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>6990</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2925</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>14132</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5006</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10339</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>6990</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3020</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>13905</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539852</t>
+          <t>539641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,82 +4753,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>544134</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>538164</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>547197</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1089037</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1081895</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1093102</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>98,71%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>544134</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>538801</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>547205</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1089037</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1082122</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1093007</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45478</t>
+          <t>44824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75482</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71935</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113556</t>
+          <t>110624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3332140</t>
+          <t>3332794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3355932</t>
+          <t>3355720</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3456618</t>
+          <t>3456293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3488625</t>
+          <t>3488307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6796162</t>
+          <t>6799094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6837783</t>
+          <t>6838264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>23405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>61411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486561</t>
+          <t>486160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502237</t>
+          <t>502049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>718138</t>
+          <t>717232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>733468</t>
+          <t>732103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1209363</t>
+          <t>1209035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1231684</t>
+          <t>1230869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55720</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>53523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>803325</t>
+          <t>746728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89057</t>
+          <t>88471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1025074</t>
+          <t>979568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2234607</t>
+          <t>2231730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2267042</t>
+          <t>2264790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1434498</t>
+          <t>1491095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2184334</t>
+          <t>2184300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3503076</t>
+          <t>3548582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4439093</t>
+          <t>4439679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>26273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41566</t>
+          <t>44061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620744</t>
+          <t>620350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638994</t>
+          <t>638615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634651</t>
+          <t>636833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651214</t>
+          <t>652175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1265520</t>
+          <t>1263025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287721</t>
+          <t>1287235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52826</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>94740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97332</t>
+          <t>98642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>930432</t>
+          <t>927631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167210</t>
+          <t>164908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1092537</t>
+          <t>1089601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3357998</t>
+          <t>3357149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3399063</t>
+          <t>3399726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2723362</t>
+          <t>2726163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3556462</t>
+          <t>3555152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6013146</t>
+          <t>6016082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6938473</t>
+          <t>6940775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_psíq_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31049</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +783,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>41388</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>29922</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>56962</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>41388</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>30530</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>55557</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1000674</t>
+          <t>1000229</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1018958</t>
+          <t>1018624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1283097</t>
+          <t>1284076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1301491</t>
+          <t>1302311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2305447</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2289873</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2316913</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>97,57%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2288</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2305447</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>2291278</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2316305</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16528</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19888</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1676885</t>
+          <t>1675848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1689691</t>
+          <t>1689678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1567785</t>
+          <t>1568401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1582517</t>
+          <t>1581698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3250423</t>
+          <t>3249520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3268399</t>
+          <t>3268730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546801</t>
+          <t>546290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461557</t>
+          <t>460942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473376</t>
+          <t>473235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1012512</t>
+          <t>1012010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1024147</t>
+          <t>1023913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>86909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3233548</t>
+          <t>3232333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3256393</t>
+          <t>3255988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3339721</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3323740</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3350673</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6444</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6586525</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6568832</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6602895</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3339721</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3325235</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3350811</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6444</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6586525</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6568379</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6601184</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>22882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>49155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57538</t>
+          <t>54249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>55698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91610</t>
+          <t>92884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>927142</t>
+          <t>925488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>952729</t>
+          <t>951761</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1280259</t>
+          <t>1283548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1309141</t>
+          <t>1309787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2220830</t>
+          <t>2219556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2256684</t>
+          <t>2256742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39162</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,47 +2729,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>51666</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>38451</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>68534</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>51666</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>38877</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>67580</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1927382</t>
+          <t>1926989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1948521</t>
+          <t>1948529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1718641</t>
+          <t>1719075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739729</t>
+          <t>1739795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,47 +2842,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3442</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3670094</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3653226</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3683309</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,97%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3442</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3670094</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3654180</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3682883</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466198</t>
+          <t>466289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479100</t>
+          <t>479314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442925</t>
+          <t>443157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455570</t>
+          <t>455677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>915142</t>
+          <t>915330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932866</t>
+          <t>932511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46786</t>
+          <t>47439</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84877</t>
+          <t>81341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58584</t>
+          <t>58640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92279</t>
+          <t>93158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112158</t>
+          <t>113785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160047</t>
+          <t>166711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3334905</t>
+          <t>3338441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3372996</t>
+          <t>3372343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3461951</t>
+          <t>3461072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3495646</t>
+          <t>3495590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6813965</t>
+          <t>6807301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6861854</t>
+          <t>6860227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50944</t>
+          <t>52242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>731979</t>
+          <t>731582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>746723</t>
+          <t>746017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>960057</t>
+          <t>960033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>979627</t>
+          <t>979367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1698063</t>
+          <t>1696765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1722112</t>
+          <t>1722132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>26743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>42020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31368</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61181</t>
+          <t>61629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2051178</t>
+          <t>2049642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2068010</t>
+          <t>2067323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1946740</t>
+          <t>1946280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1969599</t>
+          <t>1970487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4003504</t>
+          <t>4003056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4033317</t>
+          <t>4032955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539641</t>
+          <t>539498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538164</t>
+          <t>538036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547197</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1081895</t>
+          <t>1082037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1093102</t>
+          <t>1093023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43793</t>
+          <t>43321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75807</t>
+          <t>74206</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>72408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110624</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3332794</t>
+          <t>3331303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3355720</t>
+          <t>3355668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3456293</t>
+          <t>3457894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3488307</t>
+          <t>3488779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6799094</t>
+          <t>6798904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6838264</t>
+          <t>6837310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>22551</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28778</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>32557</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38276</t>
+          <t>41323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>55107</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39577</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>69550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>495233</t>
+          <t>555978</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486160</t>
+          <t>546350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502049</t>
+          <t>563305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>725680</t>
+          <t>789481</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>717232</t>
+          <t>780715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>732103</t>
+          <t>796837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1220913</t>
+          <t>1345460</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1209035</t>
+          <t>1331017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1230869</t>
+          <t>1355945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58597</t>
+          <t>59439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>258168</t>
+          <t>63876</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53523</t>
+          <t>50598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>746728</t>
+          <t>81251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>297245</t>
+          <t>106445</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88471</t>
+          <t>88314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>979568</t>
+          <t>129628</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2251250</t>
+          <t>2187997</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2231730</t>
+          <t>2171127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2264790</t>
+          <t>2199730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1979655</t>
+          <t>2107516</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1491095</t>
+          <t>2090141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2184300</t>
+          <t>2120794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4230905</t>
+          <t>4295514</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3548582</t>
+          <t>4272331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4439679</t>
+          <t>4313645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,22 +6223,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23630</t>
+          <t>24808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29210</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>632420</t>
+          <t>695610</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620350</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638615</t>
+          <t>702744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>645456</t>
+          <t>718541</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636833</t>
+          <t>710069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652175</t>
+          <t>724523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1277876</t>
+          <t>1414151</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1263025</t>
+          <t>1401347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1287235</t>
+          <t>1424220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52163</t>
+          <t>64925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94740</t>
+          <t>102464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>303003</t>
+          <t>112768</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98642</t>
+          <t>95796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>927631</t>
+          <t>133577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>375988</t>
+          <t>193866</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164908</t>
+          <t>169105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1089601</t>
+          <t>223413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3378904</t>
+          <t>3439585</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3357149</t>
+          <t>3418219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3399726</t>
+          <t>3455758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3350791</t>
+          <t>3615539</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2726163</t>
+          <t>3594730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3555152</t>
+          <t>3632511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6729695</t>
+          <t>7055124</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6016082</t>
+          <t>7025577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6940775</t>
+          <t>7079885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_psíq_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
